--- a/DateBase/orders/Nha Thu_2026-3-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -619,12 +619,386 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C21" t="str">
+        <v>275_长相思_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>11</v>
+      </c>
+      <c r="C26" t="str">
+        <v>759_芍药红富士_Kansas_undefined_10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>12</v>
+      </c>
+      <c r="C29" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>839_洋牡丹洋葱_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>13</v>
+      </c>
+      <c r="C33" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>14</v>
+      </c>
+      <c r="C36" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>15</v>
+      </c>
+      <c r="C40" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>16</v>
+      </c>
+      <c r="C42" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>17</v>
+      </c>
+      <c r="C44" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>18</v>
+      </c>
+      <c r="C45" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>19</v>
+      </c>
+      <c r="C46" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>20</v>
+      </c>
+      <c r="C47" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>21</v>
+      </c>
+      <c r="C48" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>22</v>
+      </c>
+      <c r="C49" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>23</v>
+      </c>
+      <c r="C51" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>24</v>
+      </c>
+      <c r="C52" t="str">
+        <v>275_长相思_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>25</v>
+      </c>
+      <c r="C56" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>26</v>
+      </c>
+      <c r="C59" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -679,7 +1053,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>034330454510503020401415269615427150</v>
+        <v>03433045451050302040141526961542715322581510015050504030205291511101915381010.526404037394082634171214502120508190</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-3.xlsx
@@ -995,6 +995,9 @@
       <c r="C61" t="str">
         <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F61" t="str">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1053,7 +1056,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03433045451050302040141526961542715322581510015050504030205291511101915381010.526404037394082634171214502120508190</v>
+        <v>03433045451050302040141526961542715322581510015050504030205291511101915381010.526404037394082634171214502120508197</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -999,9 +999,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>27</v>
+      </c>
+      <c r="C62" t="str">
+        <v>872_洋牡丹棉花糖_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L62"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1056,7 +1067,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03433045451050302040141526961542715322581510015050504030205291511101915381010.526404037394082634171214502120508197</v>
+        <v>03433045451050302040141526961542715322581510015050504030205291511101915381010.52640403739408263417121450212050819730</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-3.xlsx
@@ -1069,6 +1069,9 @@
       <c r="G2" t="str">
         <v>03433045451050302040141526961542715322581510015050504030205291511101915381010.52640403739408263417121450212050819730</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
